--- a/observations-summary.xlsx
+++ b/observations-summary.xlsx
@@ -47,19 +47,19 @@
     <t>Method</t>
   </si>
   <si>
-    <t>inera-ehds-observation-lab</t>
+    <t>SEEHDSObservationLab</t>
   </si>
   <si>
     <t>SE EHDS Observation – Laboratoriesvar (GetLaboratoryOrderOutcome)</t>
   </si>
   <si>
-    <t>null#laboratory</t>
+    <t>null#laboratory, null#vital-signs</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>http://hl7.org/fhir/uv/ips/ValueSet/results-laboratory-observations-uv-ips (preferred)</t>
+    <t>http://hl7.eu/fhir/base/ValueSet/lab-obsCode-eu-lab (preferred)</t>
   </si>
   <si>
     <t>dateTimeĵ, Periodĵ</t>
